--- a/reports/output/report_d4ec36f3-65a5-475a-aa9c-7a88fcce85c2.xlsx
+++ b/reports/output/report_d4ec36f3-65a5-475a-aa9c-7a88fcce85c2.xlsx
@@ -780,7 +780,7 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>June 26, 2026 09:43 UTC</t>
+          <t>August 09, 2026 18:28 UTC</t>
         </is>
       </c>
     </row>
@@ -861,7 +861,7 @@
     <row r="17" ht="120" customHeight="1">
       <c r="A17" s="14" t="inlineStr">
         <is>
-          <t>The security assessment of http://host.docker.internal:8888 revealed a moderate risk posture with 25 findings, including 3 medium-severity issues. An attacker could potentially exploit these vulnerabilities to manipulate user interactions or steal sensitive information. The primary concern is the lack of proper security configurations, which could lead to a data breach or compliance issues. The business risk is relatively low to moderate, but it's essential to address these vulnerabilities to protect our reputation and prevent potential financial losses. We recommend prioritizing the medium-severity issues, such as missing anti-clickjacking headers and content security policy headers, as they pose the most significant risk. By fixing these issues first, we can significantly improve our overall security posture and reduce the risk of a security incident.</t>
+          <t>The security assessment of http://host.docker.internal:8888 revealed a total of 25 findings, with 3 medium-severity vulnerabilities and 22 low-severity vulnerabilities. The most critical issues found were related to security misconfigurations, including missing anti-clickjacking headers and content security policy headers not being set. An attacker could realistically use these vulnerabilities to steal credentials or embed malicious content, potentially leading to unauthorized access to sensitive data, data theft, or reputational damage. The business risk associated with these vulnerabilities is significant, as a successful attack could result in a data breach, compliance issues, financial loss, and damage to the company's reputation. To mitigate these risks, we recommend prioritizing the remediation of the medium-severity vulnerabilities, starting with the missing anti-clickjacking header and content security policy header issues on the login page, as these pose the greatest threat to the security of the application and its users.</t>
         </is>
       </c>
     </row>
@@ -977,12 +977,12 @@
       </c>
       <c r="F2" s="18" t="inlineStr">
         <is>
-          <t>Add X-Frame-Options: DENY header in your web server config. For Nginx: add_header X-Frame-Options DENY; For Apache: Header always set X-Frame-Options DENY. Alternatively, consider using the Content-Security-Policy header with the frame-ancestors directive to define allowed framing sources.</t>
+          <t>Add the X-Frame-Options header with the value DENY to your Nginx configuration: add_header X-Frame-Options DENY; Ensure this is applied to all web pages, including the login page at http://host.docker.internal:8888/login.php.</t>
         </is>
       </c>
       <c r="G2" s="18" t="inlineStr">
         <is>
-          <t>Without this header, attackers can embed your login page in an invisible iframe to trick users into submitting credentials to a malicious site, leading to potential data breaches and financial losses.</t>
+          <t>Without this header, attackers can embed your login page in an invisible iframe to steal credentials, potentially leading to unauthorized access to sensitive data.</t>
         </is>
       </c>
     </row>
@@ -1012,12 +1012,12 @@
       </c>
       <c r="F3" s="20" t="inlineStr">
         <is>
-          <t>Configure your web server to set the Content-Security-Policy header with a suitable policy, such as default-src 'self'; script-src 'self' https://cdn.example.com; object-src 'none'. For Nginx: add_header Content-Security-Policy 'default-src self; script-src self https://cdn.example.com; object-src none'; For Apache: Header always set Content-Security-Policy 'default-src self; script-src self https://cdn.example.com; object-src none'</t>
+          <t>Configure your web server to set the Content-Security-Policy header with a suitable policy, such as default-src 'self';, to define which sources of content are allowed to be executed within a web page, and apply this to the login page at http://host.docker.internal:8888/login.php.</t>
         </is>
       </c>
       <c r="G3" s="20" t="inlineStr">
         <is>
-          <t>Without a Content Security Policy, your website may be vulnerable to cross-site scripting (XSS) attacks, which can compromise user data and damage your company's reputation.</t>
+          <t>Without a Content Security Policy, your application is vulnerable to cross-site scripting attacks, which could result in data theft, financial loss, or reputational damage.</t>
         </is>
       </c>
     </row>
@@ -1047,12 +1047,12 @@
       </c>
       <c r="F4" s="18" t="inlineStr">
         <is>
-          <t>Configure your web server to set the Content-Security-Policy header with a suitable policy, such as default-src 'self'; script-src 'none'; object-src 'none'. For Nginx: add_header Content-Security-Policy 'default-src self; script-src none; object-src none'; For Apache: Header always set Content-Security-Policy 'default-src self; script-src none; object-src none'</t>
+          <t>Add a Content-Security-Policy header to the sitemap.xml page at http://host.docker.internal:8888/sitemap.xml with a policy that restricts content sources, such as default-src 'self'; script-src 'self';, to prevent cross-site scripting attacks and ensure the integrity of your application's content.</t>
         </is>
       </c>
       <c r="G4" s="18" t="inlineStr">
         <is>
-          <t>Without a Content Security Policy, your sitemap may be vulnerable to cross-site scripting (XSS) attacks, which can compromise user data and damage your company's reputation, potentially leading to compliance issues and financial losses.</t>
+          <t>The absence of a Content Security Policy on the sitemap.xml page exposes your application to cross-site scripting vulnerabilities, potentially allowing attackers to manipulate your site's content, compromising user trust and your business's reputation.</t>
         </is>
       </c>
     </row>
@@ -1087,7 +1087,7 @@
       </c>
       <c r="G5" s="20" t="inlineStr">
         <is>
-          <t>This issue represents a low-severity misconfiguration that could aid attackers in reconnaissance.</t>
+          <t>Low-severity misconfiguration that could aid attackers in reconnaissance or initial exploitation attempts.</t>
         </is>
       </c>
     </row>
@@ -1122,7 +1122,7 @@
       </c>
       <c r="G6" s="23" t="inlineStr">
         <is>
-          <t>This issue represents a low-severity misconfiguration that could aid attackers in reconnaissance.</t>
+          <t>Low-severity misconfiguration that could aid attackers in reconnaissance or initial exploitation attempts.</t>
         </is>
       </c>
     </row>
@@ -1157,7 +1157,7 @@
       </c>
       <c r="G7" s="20" t="inlineStr">
         <is>
-          <t>This issue represents a low-severity misconfiguration that could aid attackers in reconnaissance.</t>
+          <t>Low-severity misconfiguration that could aid attackers in reconnaissance or initial exploitation attempts.</t>
         </is>
       </c>
     </row>
@@ -1192,7 +1192,7 @@
       </c>
       <c r="G8" s="23" t="inlineStr">
         <is>
-          <t>This issue represents a low-severity misconfiguration that could aid attackers in reconnaissance.</t>
+          <t>Low-severity misconfiguration that could aid attackers in reconnaissance or initial exploitation attempts.</t>
         </is>
       </c>
     </row>
@@ -1227,7 +1227,7 @@
       </c>
       <c r="G9" s="20" t="inlineStr">
         <is>
-          <t>This issue represents a low-severity misconfiguration that could aid attackers in reconnaissance.</t>
+          <t>Low-severity misconfiguration that could aid attackers in reconnaissance or initial exploitation attempts.</t>
         </is>
       </c>
     </row>
@@ -1262,7 +1262,7 @@
       </c>
       <c r="G10" s="23" t="inlineStr">
         <is>
-          <t>This issue represents a low-severity misconfiguration that could aid attackers in reconnaissance.</t>
+          <t>Low-severity misconfiguration that could aid attackers in reconnaissance or initial exploitation attempts.</t>
         </is>
       </c>
     </row>
@@ -1298,7 +1298,7 @@
       </c>
       <c r="G11" s="20" t="inlineStr">
         <is>
-          <t>This issue represents a low-severity misconfiguration that could aid attackers in reconnaissance.</t>
+          <t>Low-severity misconfiguration that could aid attackers in reconnaissance or initial exploitation attempts.</t>
         </is>
       </c>
     </row>
@@ -1333,7 +1333,7 @@
       </c>
       <c r="G12" s="23" t="inlineStr">
         <is>
-          <t>This issue represents a low-severity misconfiguration that could aid attackers in reconnaissance.</t>
+          <t>Low-severity misconfiguration that could aid attackers in reconnaissance or initial exploitation attempts.</t>
         </is>
       </c>
     </row>
@@ -1368,7 +1368,7 @@
       </c>
       <c r="G13" s="20" t="inlineStr">
         <is>
-          <t>This issue represents a low-severity misconfiguration that could aid attackers in reconnaissance.</t>
+          <t>Low-severity misconfiguration that could aid attackers in reconnaissance or initial exploitation attempts.</t>
         </is>
       </c>
     </row>
@@ -1403,7 +1403,7 @@
       </c>
       <c r="G14" s="23" t="inlineStr">
         <is>
-          <t>This issue represents a low-severity misconfiguration that could aid attackers in reconnaissance.</t>
+          <t>Low-severity misconfiguration that could aid attackers in reconnaissance or initial exploitation attempts.</t>
         </is>
       </c>
     </row>
@@ -1439,7 +1439,7 @@
       </c>
       <c r="G15" s="20" t="inlineStr">
         <is>
-          <t>This issue represents a low-severity misconfiguration that could aid attackers in reconnaissance.</t>
+          <t>Low-severity misconfiguration that could aid attackers in reconnaissance or initial exploitation attempts.</t>
         </is>
       </c>
     </row>
@@ -1476,7 +1476,7 @@
       </c>
       <c r="G16" s="23" t="inlineStr">
         <is>
-          <t>This issue represents a low-severity misconfiguration that could aid attackers in reconnaissance.</t>
+          <t>Low-severity misconfiguration that could aid attackers in reconnaissance or initial exploitation attempts.</t>
         </is>
       </c>
     </row>
@@ -1511,7 +1511,7 @@
       </c>
       <c r="G17" s="20" t="inlineStr">
         <is>
-          <t>This issue represents a low-severity misconfiguration that could aid attackers in reconnaissance.</t>
+          <t>Low-severity misconfiguration that could aid attackers in reconnaissance or initial exploitation attempts.</t>
         </is>
       </c>
     </row>
@@ -1546,7 +1546,7 @@
       </c>
       <c r="G18" s="23" t="inlineStr">
         <is>
-          <t>This issue represents a low-severity misconfiguration that could aid attackers in reconnaissance.</t>
+          <t>Low-severity misconfiguration that could aid attackers in reconnaissance or initial exploitation attempts.</t>
         </is>
       </c>
     </row>
@@ -1582,7 +1582,7 @@
       </c>
       <c r="G19" s="20" t="inlineStr">
         <is>
-          <t>This issue represents a low-severity misconfiguration that could aid attackers in reconnaissance.</t>
+          <t>Low-severity misconfiguration that could aid attackers in reconnaissance or initial exploitation attempts.</t>
         </is>
       </c>
     </row>
@@ -1617,7 +1617,7 @@
       </c>
       <c r="G20" s="23" t="inlineStr">
         <is>
-          <t>This issue represents a low-severity misconfiguration that could aid attackers in reconnaissance.</t>
+          <t>Low-severity misconfiguration that could aid attackers in reconnaissance or initial exploitation attempts.</t>
         </is>
       </c>
     </row>
@@ -1652,7 +1652,7 @@
       </c>
       <c r="G21" s="20" t="inlineStr">
         <is>
-          <t>This issue represents a low-severity misconfiguration that could aid attackers in reconnaissance.</t>
+          <t>Low-severity misconfiguration that could aid attackers in reconnaissance or initial exploitation attempts.</t>
         </is>
       </c>
     </row>
@@ -1687,7 +1687,7 @@
       </c>
       <c r="G22" s="23" t="inlineStr">
         <is>
-          <t>This issue represents a low-severity misconfiguration that could aid attackers in reconnaissance.</t>
+          <t>Low-severity misconfiguration that could aid attackers in reconnaissance or initial exploitation attempts.</t>
         </is>
       </c>
     </row>
@@ -1722,7 +1722,7 @@
       </c>
       <c r="G23" s="20" t="inlineStr">
         <is>
-          <t>This issue represents a low-severity misconfiguration that could aid attackers in reconnaissance.</t>
+          <t>Low-severity misconfiguration that could aid attackers in reconnaissance or initial exploitation attempts.</t>
         </is>
       </c>
     </row>
@@ -1758,7 +1758,7 @@
       </c>
       <c r="G24" s="23" t="inlineStr">
         <is>
-          <t>This issue represents a low-severity misconfiguration that could aid attackers in reconnaissance.</t>
+          <t>Low-severity misconfiguration that could aid attackers in reconnaissance or initial exploitation attempts.</t>
         </is>
       </c>
     </row>
@@ -1793,7 +1793,7 @@
       </c>
       <c r="G25" s="20" t="inlineStr">
         <is>
-          <t>This issue represents a low-severity misconfiguration that could aid attackers in reconnaissance.</t>
+          <t>Low-severity misconfiguration that could aid attackers in reconnaissance or initial exploitation attempts.</t>
         </is>
       </c>
     </row>
@@ -1829,7 +1829,7 @@
       </c>
       <c r="G26" s="23" t="inlineStr">
         <is>
-          <t>This issue represents a low-severity misconfiguration that could aid attackers in reconnaissance.</t>
+          <t>Low-severity misconfiguration that could aid attackers in reconnaissance or initial exploitation attempts.</t>
         </is>
       </c>
     </row>
@@ -1918,7 +1918,7 @@
       </c>
       <c r="E3" s="20" t="inlineStr">
         <is>
-          <t>Add X-Frame-Options: DENY header in your web server config. For Nginx: add_header X-Frame-Options DENY; For Apache: Header always set X-Frame-Options DENY. Alternatively, consider using the Content-Security-Policy header with the frame-ancestors directive to define allowed framing sources.</t>
+          <t>Add the X-Frame-Options header with the value DENY to your Nginx configuration: add_header X-Frame-Options DENY; Ensure this is applied to all web pages, including the login page at http://host.docker.internal:8888/login.php.</t>
         </is>
       </c>
       <c r="F3" s="19" t="n">
@@ -1948,7 +1948,7 @@
       </c>
       <c r="E4" s="27" t="inlineStr">
         <is>
-          <t>Configure your web server to set the Content-Security-Policy header with a suitable policy, such as default-src 'self'; script-src 'self' https://cdn.example.com; object-src 'none'. For Nginx: add_header Content-Security-Policy 'default-src self; script-src self https://cdn.example.com; object-src n</t>
+          <t>Configure your web server to set the Content-Security-Policy header with a suitable policy, such as default-src 'self';, to define which sources of content are allowed to be executed within a web page, and apply this to the login page at http://host.docker.internal:8888/login.php.</t>
         </is>
       </c>
       <c r="F4" s="19" t="n">
@@ -1978,7 +1978,7 @@
       </c>
       <c r="E5" s="20" t="inlineStr">
         <is>
-          <t>Configure your web server to set the Content-Security-Policy header with a suitable policy, such as default-src 'self'; script-src 'none'; object-src 'none'. For Nginx: add_header Content-Security-Policy 'default-src self; script-src none; object-src none'; For Apache: Header always set Content-Secu</t>
+          <t>Add a Content-Security-Policy header to the sitemap.xml page at http://host.docker.internal:8888/sitemap.xml with a policy that restricts content sources, such as default-src 'self'; script-src 'self';, to prevent cross-site scripting attacks and ensure the integrity of your application's content.</t>
         </is>
       </c>
       <c r="F5" s="19" t="n">
